--- a/src/ExcelsiorOpenXml.Tests/ComplexTypeWithCustomEnumerableRender.Null.verified.xlsx
+++ b/src/ExcelsiorOpenXml.Tests/ComplexTypeWithCustomEnumerableRender.Null.verified.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2f380fe02e7c4f2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Raeffa4d3a8a84b8a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/src/ExcelsiorOpenXml.Tests/ComplexTypeWithCustomEnumerableRender.Null.verified.xlsx
+++ b/src/ExcelsiorOpenXml.Tests/ComplexTypeWithCustomEnumerableRender.Null.verified.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Raeffa4d3a8a84b8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="DeterministicId2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -12,6 +12,7 @@
   <x:fonts count="1">
     <x:font>
       <x:sz val="11"/>
+      <x:name val="Aptos"/>
     </x:font>
   </x:fonts>
   <x:fills count="2">

--- a/src/ExcelsiorOpenXml.Tests/ComplexTypeWithCustomEnumerableRender.Null.verified.xlsx
+++ b/src/ExcelsiorOpenXml.Tests/ComplexTypeWithCustomEnumerableRender.Null.verified.xlsx
@@ -9,8 +9,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="1">
+  <x:fonts count="2">
     <x:font>
+      <x:sz val="11"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
       <x:sz val="11"/>
       <x:name val="Aptos"/>
     </x:font>
@@ -34,7 +39,7 @@
   </x:borders>
   <x:cellXfs count="3">
     <x:xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0"/>
-    <x:xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0"/>
+    <x:xf fontId="1" fillId="0" borderId="0" applyFont="1" applyFill="0"/>
     <x:xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyAlignment="1">
       <x:alignment horizontal="left" vertical="top" wrapText="1"/>
     </x:xf>

--- a/src/ExcelsiorOpenXml.Tests/ComplexTypeWithCustomEnumerableRender.Null.verified.xlsx
+++ b/src/ExcelsiorOpenXml.Tests/ComplexTypeWithCustomEnumerableRender.Null.verified.xlsx
@@ -12,12 +12,12 @@
   <x:fonts count="2">
     <x:font>
       <x:sz val="11"/>
-      <x:name val="Aptos"/>
+      <x:name val="Calibri"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:sz val="11"/>
-      <x:name val="Aptos"/>
+      <x:name val="Calibri"/>
     </x:font>
   </x:fonts>
   <x:fills count="2">

--- a/src/ExcelsiorOpenXml.Tests/ComplexTypeWithCustomEnumerableRender.Null.verified.xlsx
+++ b/src/ExcelsiorOpenXml.Tests/ComplexTypeWithCustomEnumerableRender.Null.verified.xlsx
@@ -9,10 +9,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="1">
+  <x:fonts count="2">
     <x:font>
       <x:sz val="11"/>
-      <x:name val="Aptos"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:name val="Calibri"/>
     </x:font>
   </x:fonts>
   <x:fills count="2">
@@ -34,7 +39,7 @@
   </x:borders>
   <x:cellXfs count="3">
     <x:xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0"/>
-    <x:xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0"/>
+    <x:xf fontId="1" fillId="0" borderId="0" applyFont="1" applyFill="0"/>
     <x:xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyAlignment="1">
       <x:alignment horizontal="left" vertical="top" wrapText="1"/>
     </x:xf>

--- a/src/ExcelsiorOpenXml.Tests/ComplexTypeWithCustomEnumerableRender.Null.verified.xlsx
+++ b/src/ExcelsiorOpenXml.Tests/ComplexTypeWithCustomEnumerableRender.Null.verified.xlsx
@@ -79,5 +79,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
+  <x:autoFilter ref="A1:B2"/>
 </x:worksheet>
 </file>
--- a/src/ExcelsiorOpenXml.Tests/ComplexTypeWithCustomEnumerableRender.Null.verified.xlsx
+++ b/src/ExcelsiorOpenXml.Tests/ComplexTypeWithCustomEnumerableRender.Null.verified.xlsx
@@ -72,11 +72,7 @@
           <t xml:space="preserve">John Doe</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">● </t>
-        </is>
-      </c>
+      <c r="B2" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:B2"/>

--- a/src/ExcelsiorOpenXml.Tests/ComplexTypeWithCustomEnumerableRender.Null.verified.xlsx
+++ b/src/ExcelsiorOpenXml.Tests/ComplexTypeWithCustomEnumerableRender.Null.verified.xlsx
@@ -75,6 +75,6 @@
       <c r="B2" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B2"/>
+  <autoFilter ref="A1:A2"/>
 </worksheet>
 </file>